--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486711_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486711_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.319</v>
+        <v>7.4072</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5949</v>
+        <v>4.8569</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7241</v>
+        <v>2.5503</v>
       </c>
       <c r="G2" t="n">
         <v>4.4703</v>
@@ -610,13 +610,13 @@
         <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3018</v>
+        <v>-1.2136</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5523</v>
+        <v>-0.2903</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.9233</v>
       </c>
       <c r="V2" t="n">
         <v>2.4128</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.703</v>
+        <v>3.0891</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3992</v>
+        <v>1.6612</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3037</v>
+        <v>1.4279</v>
       </c>
       <c r="G3" t="n">
         <v>0.2921</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6897</v>
+        <v>-0.3035</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0005</v>
+        <v>0.2616</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6892</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>1.5559</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8299</v>
+        <v>0.2631</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.1881</v>
+        <v>-2.9603</v>
       </c>
       <c r="F4" t="n">
-        <v>4.018</v>
+        <v>3.2234</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7127</v>
@@ -766,13 +766,13 @@
         <v>2.8962</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9602000000000001</v>
+        <v>-0.6066</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7439</v>
+        <v>-0.0282</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2162</v>
+        <v>-0.5784</v>
       </c>
       <c r="V4" t="n">
         <v>2.741</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1089</v>
+        <v>-1.1566</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6314</v>
+        <v>-0.2842</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4775</v>
+        <v>-0.8724</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0925</v>
+        <v>-2.4915</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4274</v>
+        <v>-2.9029</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5199</v>
+        <v>0.4114</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9134</v>
+        <v>-1.953</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2624</v>
+        <v>-2.0751</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6511</v>
+        <v>0.1221</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8209</v>
+        <v>-0.5385</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6898</v>
+        <v>-0.8278</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1311</v>
+        <v>0.2893</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.8962</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9804</v>
+        <v>0.2344</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3513</v>
+        <v>0.4411</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6291</v>
+        <v>-0.2067</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2856</v>
+        <v>0.3282</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3304</v>
+        <v>-1.6703</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2842</v>
+        <v>-2.8901</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0462</v>
+        <v>1.2198</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4915</v>
+        <v>-0.0527</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9029</v>
+        <v>-0.1455</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4114</v>
+        <v>0.0927</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.953</v>
+        <v>-0.6102</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.0751</v>
+        <v>0.6828</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1221</v>
+        <v>-1.293</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5385</v>
+        <v>0.5574</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8278</v>
+        <v>-0.8283</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2893</v>
+        <v>1.3857</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0606</v>
+        <v>-0.3586</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4411</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3805</v>
+        <v>-0.8823</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7984</v>
+        <v>-1.6743</v>
       </c>
       <c r="E8" t="n">
         <v>-0.8322000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.842</v>
       </c>
       <c r="G8" t="n">
         <v>-1.794</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3584</v>
+        <v>0.4826</v>
       </c>
       <c r="T8" t="n">
         <v>0.1377</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2208</v>
+        <v>0.3449</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9421</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8453</v>
+        <v>-2.1308</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7175</v>
+        <v>-1.3554</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8721</v>
+        <v>-0.7754</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0527</v>
+        <v>0.0925</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1455</v>
+        <v>-0.4274</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0927</v>
+        <v>0.5199</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6102</v>
+        <v>0.9134</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6828</v>
+        <v>0.2624</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.293</v>
+        <v>0.6511</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5574</v>
+        <v>-0.8209</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8283</v>
+        <v>-0.6898</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3857</v>
+        <v>-0.1311</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5446</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0892</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5336</v>
+        <v>0.9584</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3037</v>
+        <v>0.6274</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2299</v>
+        <v>0.3311</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9021</v>
+        <v>-2.2676</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2183</v>
+        <v>-2.9563</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3162</v>
+        <v>0.6887</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8884</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0137</v>
+        <v>-1.3792</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1588</v>
+        <v>-0.8968</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8548</v>
+        <v>-0.4824</v>
       </c>
       <c r="V10" t="n">
         <v>0.6138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4787</v>
+        <v>-3.68</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6031</v>
+        <v>-2.7548</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8756</v>
+        <v>-0.9252</v>
       </c>
       <c r="G11" t="n">
         <v>-0.08</v>
@@ -1312,13 +1312,13 @@
         <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7502</v>
+        <v>-0.9516</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3038</v>
+        <v>-0.4555</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4464</v>
+        <v>-0.4961</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4554</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4265</v>
+        <v>-3.9425</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3596</v>
+        <v>-2.0493</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0669</v>
+        <v>-1.8931</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2497</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2081</v>
+        <v>-0.724</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2208</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9873</v>
+        <v>-0.8135</v>
       </c>
       <c r="V12" t="n">
         <v>-2.741</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.210699999999999</v>
+        <v>-6.934999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.8057</v>
+        <v>-10.5299</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5948</v>
+        <v>3.5951</v>
       </c>
       <c r="G13" t="n">
         <v>-3.621</v>
@@ -1438,10 +1438,10 @@
         <v>-11.0362</v>
       </c>
       <c r="I13" t="n">
-        <v>7.4152</v>
+        <v>7.415199999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.472999999999999</v>
+        <v>-5.473</v>
       </c>
       <c r="K13" t="n">
         <v>-5.1683</v>
@@ -1459,7 +1459,7 @@
         <v>7.719500000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9655000000000002</v>
+        <v>-0.9654999999999998</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.4463</v>
@@ -1468,16 +1468,16 @@
         <v>14.4808</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.1375</v>
+        <v>-3.8617</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1341000000000001</v>
+        <v>0.4101</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.271500000000001</v>
+        <v>-4.271700000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5132</v>
+        <v>1.513200000000001</v>
       </c>
       <c r="W13" t="n">
         <v>9.9793</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7206</v>
+        <v>7.1963</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0792</v>
+        <v>3.3894</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6415</v>
+        <v>3.8068</v>
       </c>
       <c r="G14" t="n">
         <v>5.7577</v>
@@ -1546,13 +1546,13 @@
         <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1862</v>
+        <v>1.6619</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7442</v>
+        <v>1.0545</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4421</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.1628</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4821</v>
+        <v>5.4587</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8539</v>
+        <v>3.5437</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6281</v>
+        <v>1.915</v>
       </c>
       <c r="G15" t="n">
         <v>3.9913</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3199</v>
+        <v>0.2966</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3031</v>
+        <v>-0.0072</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0169</v>
+        <v>0.3037</v>
       </c>
       <c r="V15" t="n">
         <v>0.2055</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.728</v>
+        <v>0.8618</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1356</v>
+        <v>-0.7562</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8636</v>
+        <v>1.6179</v>
       </c>
       <c r="G16" t="n">
         <v>0.8704</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4937</v>
+        <v>1.6275</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5992</v>
+        <v>0.9787</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8945</v>
+        <v>0.6488</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6361</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>L. BUENO CASTILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1104</v>
+        <v>0.4258</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2367</v>
+        <v>1.2092</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1263</v>
+        <v>-0.7834</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6364</v>
+        <v>0.295</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8964</v>
+        <v>-1.0409</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.26</v>
+        <v>1.336</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3474</v>
+        <v>-0.3591</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0346</v>
+        <v>-1.6612</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6872</v>
+        <v>1.3022</v>
       </c>
       <c r="M17" t="n">
-        <v>0.289</v>
+        <v>0.6541</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1382</v>
+        <v>0.6203</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4272</v>
+        <v>0.0338</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4081</v>
+        <v>0.9377</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8547</v>
+        <v>0.7581</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4466</v>
+        <v>0.1796</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5133</v>
+        <v>-0.6138</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5133</v>
+        <v>-3.3548</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0371</v>
+        <v>0.1905</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6161</v>
+        <v>-2.9264</v>
       </c>
       <c r="F18" t="n">
-        <v>2.579</v>
+        <v>3.1168</v>
       </c>
       <c r="G18" t="n">
         <v>-3.9338</v>
@@ -1858,13 +1858,13 @@
         <v>2.7031</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1859</v>
+        <v>1.4135</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1853</v>
+        <v>0.875</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0007</v>
+        <v>0.5385</v>
       </c>
       <c r="V18" t="n">
         <v>2.9038</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. BUENO CASTILLO</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4953</v>
+        <v>-0.1943</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5887</v>
+        <v>-0.2804</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.084</v>
+        <v>0.0861</v>
       </c>
       <c r="G19" t="n">
-        <v>0.295</v>
+        <v>0.6364</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0409</v>
+        <v>0.8964</v>
       </c>
       <c r="I19" t="n">
-        <v>1.336</v>
+        <v>-0.26</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3591</v>
+        <v>0.3474</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6612</v>
+        <v>1.0346</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3022</v>
+        <v>-0.6872</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6541</v>
+        <v>0.289</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6203</v>
+        <v>-0.1382</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0338</v>
+        <v>0.4272</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0166</v>
+        <v>0.1033</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1375</v>
+        <v>0.3376</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.121</v>
+        <v>-0.2342</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6138</v>
+        <v>-1.5133</v>
       </c>
       <c r="W19" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.3548</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6888</v>
+        <v>-0.6143</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5383</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8495</v>
+        <v>0.924</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6281</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4469</v>
+        <v>-0.3724</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2261</v>
+        <v>-0.1516</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9445</v>
+        <v>-1.7032</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8321</v>
+        <v>-0.7287</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1124</v>
+        <v>-0.9745</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7773</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6619</v>
+        <v>-0.4206</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2484</v>
+        <v>-0.145</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4136</v>
+        <v>-0.2757</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4707</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6646</v>
+        <v>-2.342</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.2312</v>
+        <v>-5.5073</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5667</v>
+        <v>3.1653</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5904</v>
@@ -2170,13 +2170,13 @@
         <v>2.7031</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3641</v>
+        <v>0.9584</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0833</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2808</v>
+        <v>0.3178</v>
       </c>
       <c r="V22" t="n">
         <v>0.4485</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.210800000000001</v>
+        <v>9.279300000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.594800000000001</v>
+        <v>-3.595000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>10.8057</v>
+        <v>12.874</v>
       </c>
       <c r="G23" t="n">
         <v>3.621199999999999</v>
@@ -2248,13 +2248,13 @@
         <v>15.4463</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1375</v>
+        <v>6.2059</v>
       </c>
       <c r="T23" t="n">
-        <v>4.271599999999999</v>
+        <v>4.2716</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1339000000000001</v>
+        <v>1.9343</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5133</v>
